--- a/plyometrics/②プライオメトリクス内容まとめ.xlsx
+++ b/plyometrics/②プライオメトリクス内容まとめ.xlsx
@@ -604,7 +604,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSCA S&amp;C教本 第18章 プライオメトリクス　概要・基本概念</t>
+          <t>S&amp;C領域 プライオメトリクス　概要・基本概念</t>
         </is>
       </c>
     </row>
